--- a/Revised_data/Consensus.xlsx
+++ b/Revised_data/Consensus.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kiran Kumar\Documents\Temp\Revised_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kiran Kumar\Documents\Projects\QNArag_IntellimarkAI\Revised_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7E620B-C0C8-48C9-AE65-AF837B4BC825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C77F84-0485-4955-8A1D-77635686CB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -791,7 +791,7 @@
   <dimension ref="A1:AM55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.88671875" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" x14ac:dyDescent="0.3">
